--- a/data/fund_whitelist.xlsx
+++ b/data/fund_whitelist.xlsx
@@ -42,7 +42,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -74,12 +80,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -445,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B84"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -463,6 +470,16 @@
           <t>基金简称</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>上市日期</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>规模</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -475,6 +492,16 @@
           <t>嘉实沪深300增强A</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2014-12-26</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>12.44亿</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -487,6 +514,16 @@
           <t>景顺长城沪深300增强A</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2013-10-29</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>28.94亿</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -499,6 +536,16 @@
           <t>华安沪深300量化增强A</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2013-09-27</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>4.82亿</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -511,6 +558,16 @@
           <t>国泰沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2014-05-19</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7112.58万</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -523,6 +580,16 @@
           <t>华夏沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2015-02-10</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>22.81亿</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -535,6 +602,16 @@
           <t>华泰柏瑞沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2015-03-24</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3.46亿</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -547,6 +624,16 @@
           <t>创金合信沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2015-12-31</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1.13亿</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -559,6 +646,16 @@
           <t>万家沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2016-09-26</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4.44亿</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -571,6 +668,16 @@
           <t>中金沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2016-07-22</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>10.69亿</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -583,6 +690,16 @@
           <t>华宝沪深300增强策略ETF联接A</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2016-12-09</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>5.95亿</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -595,6 +712,16 @@
           <t>汇安沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2017-01-25</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>9869.45万</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -607,6 +734,16 @@
           <t>安信量化精选沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2017-03-16</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>9.85亿</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -619,6 +756,16 @@
           <t>招商沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2017-02-10</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4.28亿</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -631,6 +778,16 @@
           <t>海富通沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2017-05-10</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>13.73亿</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -643,6 +800,16 @@
           <t>富荣沪深300增强A</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2018-02-11</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8.38亿</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -655,6 +822,16 @@
           <t>中银沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2017-11-24</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>5.49亿</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -667,6 +844,16 @@
           <t>平安沪深300指数量化增强A</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2017-12-26</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>9.13亿</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -679,6 +866,16 @@
           <t>长信沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2018-04-19</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>3.05亿</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -691,6 +888,16 @@
           <t>新华沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2019-12-18</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>7464.89万</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -703,6 +910,16 @@
           <t>汇添富沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2018-03-23</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>9.99亿</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -715,6 +932,16 @@
           <t>财通沪深300指数增强</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2019-01-30</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1.46亿</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -727,6 +954,16 @@
           <t>鹏华沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2018-05-25</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>15.06亿</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -739,6 +976,16 @@
           <t>广发沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2018-06-29</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>4.90亿</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -751,6 +998,16 @@
           <t>博道沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2019-04-26</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>12.73亿</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -763,6 +1020,16 @@
           <t>国投瑞银沪深300量化增强A</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2019-06-11</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>5.82亿</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -775,6 +1042,16 @@
           <t>银河沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2019-08-29</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2.14亿</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -787,6 +1064,16 @@
           <t>中泰沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2.87亿</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -799,6 +1086,16 @@
           <t>天弘沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2019-12-27</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>7.09亿</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -811,6 +1108,16 @@
           <t>南方沪深300增强A</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2020-04-23</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2.41亿</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -823,6 +1130,16 @@
           <t>易方达沪深300精选增强A</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2020-12-30</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>20.74亿</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -835,6 +1152,16 @@
           <t>汇添富沪深300基本面增强A</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2021-01-20</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>30.42亿</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -847,6 +1174,16 @@
           <t>博时沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2020-12-30</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>4036.62万</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -859,6 +1196,16 @@
           <t>大成沪深300增强A</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2021-02-23</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>8120.31万</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -871,6 +1218,16 @@
           <t>长江沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2021-06-02</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>6496.02万</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -883,6 +1240,16 @@
           <t>中泰沪深300指数量化优选A</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2021-07-05</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2523.15万</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -895,6 +1262,16 @@
           <t>同泰沪深300量化增强A</t>
         </is>
       </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2021-07-23</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2688.43万</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -907,6 +1284,16 @@
           <t>华安沪深300增强策略ETF联接A</t>
         </is>
       </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1280.40万</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -919,6 +1306,16 @@
           <t>中信建投沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1.29亿</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -931,6 +1328,16 @@
           <t>中欧沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2022-03-29</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>3.74亿</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -943,6 +1350,16 @@
           <t>东方沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2022-11-08</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2785.47万</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -955,6 +1372,16 @@
           <t>国泰海通沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>11.93亿</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -967,6 +1394,16 @@
           <t>中信保诚沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1.51亿</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -979,6 +1416,16 @@
           <t>国联安沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2024-01-23</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2.90亿</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -991,6 +1438,16 @@
           <t>中欧沪深300指数量化增强A</t>
         </is>
       </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>7.56亿</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1003,6 +1460,16 @@
           <t>国泰沪深300增强策略ETF联接A</t>
         </is>
       </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1519.04万</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1015,6 +1482,16 @@
           <t>富安达沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2781.16万</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1027,6 +1504,16 @@
           <t>国联沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2.42亿</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1039,6 +1526,16 @@
           <t>贝莱德沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1051,6 +1548,16 @@
           <t>博道沪深300指数量化增强A</t>
         </is>
       </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2025-01-21</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>4.10亿</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1063,6 +1570,16 @@
           <t>兴全中证沪港深300指数增强A</t>
         </is>
       </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>3143.65万</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1075,6 +1592,16 @@
           <t>鹏华沪深300指数量化增强A</t>
         </is>
       </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>4805.47万</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1087,6 +1614,16 @@
           <t>光大沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2345.43万</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1099,6 +1636,16 @@
           <t>华商沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2234.59万</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1111,6 +1658,16 @@
           <t>长信沪深300指数量化增强A</t>
         </is>
       </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1123,6 +1680,16 @@
           <t>永赢沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2647.94万</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1135,6 +1702,16 @@
           <t>华富沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1959.58万</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1147,6 +1724,16 @@
           <t>招商沪深300增强策略ETF联接A</t>
         </is>
       </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>3375.37万</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1159,6 +1746,16 @@
           <t>天弘沪深300指数量化增强A</t>
         </is>
       </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>737.52万</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1171,6 +1768,16 @@
           <t>汇添富沪深300指数量化增强A</t>
         </is>
       </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1.66亿</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1183,6 +1790,16 @@
           <t>华夏沪深300指数量化增强A</t>
         </is>
       </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>9.34亿</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1195,6 +1812,16 @@
           <t>万家沪深300指数量化增强A</t>
         </is>
       </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1372.07万</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1207,6 +1834,16 @@
           <t>泰康沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1363.58万</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1219,6 +1856,16 @@
           <t>广发沪深300指数量化增强A</t>
         </is>
       </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2.31亿</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1231,6 +1878,16 @@
           <t>德邦沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1243,6 +1900,16 @@
           <t>华泰保兴沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1255,6 +1922,16 @@
           <t>富国沪深300增强A</t>
         </is>
       </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2009-12-16</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>46.17亿</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1267,6 +1944,16 @@
           <t>易方达沪深300量化增强A</t>
         </is>
       </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2012-07-05</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>9.35亿</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1279,6 +1966,16 @@
           <t>景顺长城沪深300增强策略ETF</t>
         </is>
       </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1291,6 +1988,16 @@
           <t>宏利沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2010-04-23</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>5.39亿</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1303,6 +2010,16 @@
           <t>兴全沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2010-11-02</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>39.43亿</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1315,6 +2032,16 @@
           <t>建信沪深300增强A</t>
         </is>
       </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2011-05-06</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2.89亿</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1327,6 +2054,16 @@
           <t>浙商沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2012-05-07</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1.54亿</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1339,6 +2076,16 @@
           <t>国金沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2013-07-26</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>9469.08万</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1351,6 +2098,16 @@
           <t>长城久泰沪深300A</t>
         </is>
       </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2004-05-21</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>7.98亿</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1363,6 +2120,16 @@
           <t>申万菱信沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2004-11-29</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>8.07亿</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1375,6 +2142,16 @@
           <t>诺安沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2011-04-07</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>3.53亿</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1387,6 +2164,16 @@
           <t>国富沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2009-09-03</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2.32亿</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1399,6 +2186,16 @@
           <t>浦银安盛沪深300指数增强A</t>
         </is>
       </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2010-12-10</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2.36亿</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1411,6 +2208,16 @@
           <t>华安沪深300增强策略ETF</t>
         </is>
       </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1423,6 +2230,16 @@
           <t>国泰沪深300增强策略ETF</t>
         </is>
       </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1435,6 +2252,16 @@
           <t>招商沪深300增强策略ETF</t>
         </is>
       </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1447,6 +2274,16 @@
           <t>华宝沪深300增强策略ETF</t>
         </is>
       </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1457,6 +2294,16 @@
       <c r="B84" t="inlineStr">
         <is>
           <t>西部利得沪深300指数增强A</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2017-03-21</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2.14亿</t>
         </is>
       </c>
     </row>
@@ -1471,7 +2318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B83"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1489,6 +2336,16 @@
           <t>基金简称</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>上市日期</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>规模</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1501,6 +2358,16 @@
           <t>建信中证500指数增强A</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2014-01-27</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>33.32亿</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1513,6 +2380,16 @@
           <t>汇添富中证500指数增强A</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2015-02-16</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>13.03亿</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1525,6 +2402,16 @@
           <t>诺安中证500指数增强A</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2015-06-09</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2758.73万</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1537,6 +2424,16 @@
           <t>天弘中证500指数增强A</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2015-06-30</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>19.13亿</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1549,6 +2446,16 @@
           <t>浙商中证500指数增强A</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2016-05-11</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1.32亿</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1561,6 +2468,16 @@
           <t>创金合信中证500指数增强A</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2015-12-31</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1.80亿</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1573,6 +2490,16 @@
           <t>申万菱信中证500指数增强A</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2016-04-21</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1.33亿</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1585,6 +2512,16 @@
           <t>南方中证500增强A</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2016-11-23</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4.08亿</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1597,6 +2534,16 @@
           <t>中金中证500指数增强A</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2016-07-22</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8.87亿</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1609,6 +2556,16 @@
           <t>国泰中证500指数增强A</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2017-08-01</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8243.26万</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1621,6 +2578,16 @@
           <t>申万菱信中证500优选增强A</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2017-01-10</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>14.92亿</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1633,6 +2600,16 @@
           <t>招商中证500指数增强A</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2017-05-17</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>6.24亿</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1645,6 +2622,16 @@
           <t>长信中证500指数增强A</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2017-08-30</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2.44亿</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1657,6 +2644,16 @@
           <t>博时中证500指数增强A</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2017-09-26</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2.47亿</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1669,6 +2666,16 @@
           <t>华宝中证500指数增强A</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2018-04-19</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3092.56万</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1681,6 +2688,16 @@
           <t>安信中证500指数增强A</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2018-11-29</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1156.65万</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1693,6 +2710,16 @@
           <t>国投瑞银中证500量化增强A</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2018-08-01</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>9.74亿</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1705,6 +2732,16 @@
           <t>长城中证500指数增强A</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2018-08-13</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>8.38亿</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1717,6 +2754,16 @@
           <t>中信建投中证500增强A</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2020-05-09</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>9843.42万</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1729,6 +2776,16 @@
           <t>博道中证500指数增强A</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2019-01-03</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>14.95亿</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1741,6 +2798,16 @@
           <t>景顺长城中证500指数增强A</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2019-03-25</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>4.18亿</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1753,6 +2820,16 @@
           <t>万家中证500指数增强A</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2019-05-23</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>6.47亿</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1765,6 +2842,16 @@
           <t>富安达中证500指数增强A</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2019-11-19</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>7830.15万</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1777,6 +2864,16 @@
           <t>华夏中证500指数增强A</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2020-03-25</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>38.06亿</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1789,6 +2886,16 @@
           <t>嘉实中证500指数增强A</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2020-01-20</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>7786.00万</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1801,6 +2908,16 @@
           <t>平安中证500指数增强A</t>
         </is>
       </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2020-05-27</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1390.64万</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1813,6 +2930,16 @@
           <t>广发中证500指数增强A</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2020-10-15</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1.85亿</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1825,6 +2952,16 @@
           <t>上银中证500指数增强A</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2020-07-01</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>3629.30万</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1837,6 +2974,16 @@
           <t>招商中证500等权重指数增强A</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2020-12-23</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>4.78亿</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1849,6 +2996,16 @@
           <t>中加中证500指数增强A</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1897.09万</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1861,6 +3018,16 @@
           <t>汇安中证500增强A</t>
         </is>
       </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1873,6 +3040,16 @@
           <t>兴银中证500指数增强A</t>
         </is>
       </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2021-03-01</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2701.93万</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1885,6 +3062,16 @@
           <t>易方达中证500量化增强A</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2021-06-15</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>4.72亿</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1897,6 +3084,16 @@
           <t>汇添富中证500基本面增强A</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>4901.87万</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1909,6 +3106,16 @@
           <t>民生加银中证500指数增强A</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2021-08-10</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>3505.66万</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1921,6 +3128,16 @@
           <t>华夏中证500指数智选A</t>
         </is>
       </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2021-08-11</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>9.12亿</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1933,6 +3150,16 @@
           <t>光大中证500指数增强A</t>
         </is>
       </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2021-09-29</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1.04亿</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1945,6 +3172,16 @@
           <t>圆信永丰中证500指数增强A</t>
         </is>
       </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2021-12-01</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>9277.21万</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1957,6 +3194,16 @@
           <t>工银中证500六个月持有指数增强A</t>
         </is>
       </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2021-12-14</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>8935.54万</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1969,6 +3216,16 @@
           <t>国泰海通中证500A</t>
         </is>
       </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2021-12-15</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>24.84亿</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1981,6 +3238,16 @@
           <t>华泰柏瑞中证500指数增强A</t>
         </is>
       </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2022-04-27</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>3.20亿</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1993,6 +3260,16 @@
           <t>鹏华中证500指数增强A</t>
         </is>
       </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2022-01-11</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>10.23亿</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2005,6 +3282,16 @@
           <t>华安中证500指数增强A</t>
         </is>
       </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2022-05-24</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>4339.94万</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2017,6 +3304,16 @@
           <t>中欧中证500指数增强A</t>
         </is>
       </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>18.60亿</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2029,6 +3326,16 @@
           <t>兴业中证500指数增强A</t>
         </is>
       </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2022-06-07</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1.55亿</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2041,6 +3348,16 @@
           <t>建信中证500指数量化增强A</t>
         </is>
       </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2022-12-23</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1.09亿</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2053,6 +3370,16 @@
           <t>中金中证500ESG基准指数增强A</t>
         </is>
       </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2022-10-25</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>559.34万</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2065,6 +3392,16 @@
           <t>华泰紫金中证500指数增强A</t>
         </is>
       </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2023-02-22</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>3486.24万</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2077,6 +3414,16 @@
           <t>泰康中证500指数增强A</t>
         </is>
       </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2161.54万</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2089,6 +3436,16 @@
           <t>财通中证500指数增强A</t>
         </is>
       </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2023-07-13</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2935.08万</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2101,6 +3458,16 @@
           <t>中银中证500指数增强A</t>
         </is>
       </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2023-12-26</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2027.83万</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2113,6 +3480,16 @@
           <t>国联中证500指数增强A</t>
         </is>
       </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1.13亿</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2125,6 +3502,16 @@
           <t>大成中证500指数增强A</t>
         </is>
       </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1905.22万</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2137,6 +3524,16 @@
           <t>东方红中证500指数增强A</t>
         </is>
       </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3421.12万</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2149,6 +3546,16 @@
           <t>中信保诚中证500指数增强A</t>
         </is>
       </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>7240.92万</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2161,6 +3568,16 @@
           <t>永赢中证500指数增强A</t>
         </is>
       </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2143.25万</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2173,6 +3590,16 @@
           <t>苏新中证500指数增强A</t>
         </is>
       </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2185,6 +3612,16 @@
           <t>兴全中证500指数增强A</t>
         </is>
       </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1.10亿</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2197,6 +3634,16 @@
           <t>招商资管中证500指数增强A</t>
         </is>
       </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2209,6 +3656,16 @@
           <t>兴全中证沪港深500指数增强A</t>
         </is>
       </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>6399.46万</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2221,6 +3678,16 @@
           <t>泓德中证500指数增强A</t>
         </is>
       </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>7658.44万</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2233,6 +3700,16 @@
           <t>招商中证500增强策略ETF联接A</t>
         </is>
       </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2245,6 +3722,16 @@
           <t>天弘中证500指数量化增强A</t>
         </is>
       </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>3856.85万</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2257,6 +3744,16 @@
           <t>人保中证500指数增强A</t>
         </is>
       </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>4.35亿</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2269,6 +3766,16 @@
           <t>贝莱德中证500指数增强A</t>
         </is>
       </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2281,6 +3788,16 @@
           <t>鹏华中证500指数量化增强A</t>
         </is>
       </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>3404.98万</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2293,6 +3810,16 @@
           <t>联博中证500指数增强A</t>
         </is>
       </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2305,6 +3832,16 @@
           <t>财通资管中证500指数增强A</t>
         </is>
       </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>8088.65万</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2317,6 +3854,16 @@
           <t>广发中证500指数量化增强A</t>
         </is>
       </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>5.78亿</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2329,6 +3876,16 @@
           <t>中欧中证500指数量化增强A</t>
         </is>
       </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2341,6 +3898,16 @@
           <t>景顺长城中证500增强策略ETF</t>
         </is>
       </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2353,6 +3920,16 @@
           <t>博时中证500增强策略ETF</t>
         </is>
       </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2365,6 +3942,16 @@
           <t>富国中证500指数增强A</t>
         </is>
       </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2011-10-12</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>39.47亿</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2377,6 +3964,16 @@
           <t>宏利中证500指数增强</t>
         </is>
       </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2011-12-01</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1.75亿</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2389,6 +3986,16 @@
           <t>西部利得中证500指数增强A</t>
         </is>
       </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2015-04-15</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>10.72亿</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2401,6 +4008,16 @@
           <t>海富通中证500增强A</t>
         </is>
       </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2012-05-25</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2978.59万</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2413,6 +4030,16 @@
           <t>南方中证500增强策略ETF</t>
         </is>
       </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2425,6 +4052,16 @@
           <t>汇添富中证500增强策略ETF</t>
         </is>
       </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2437,6 +4074,16 @@
           <t>华泰柏瑞中证500增强策略ETF</t>
         </is>
       </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2449,6 +4096,16 @@
           <t>招商中证500增强策略ETF</t>
         </is>
       </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2461,6 +4118,16 @@
           <t>易方达中证500增强策略ETF</t>
         </is>
       </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2471,6 +4138,16 @@
       <c r="B83" t="inlineStr">
         <is>
           <t>中邮中证500指数增强A</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2011-11-22</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>5731.22万</t>
         </is>
       </c>
     </row>
@@ -2485,7 +4162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2503,6 +4180,16 @@
           <t>基金简称</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>上市日期</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>规模</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2515,6 +4202,16 @@
           <t>创金合信中证1000增强A</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2016-12-22</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3575.34万</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2527,6 +4224,16 @@
           <t>招商中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2017-03-03</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>10.48亿</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2539,6 +4246,16 @@
           <t>万家中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2018-01-30</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8.49亿</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2551,6 +4268,16 @@
           <t>建信中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2018-11-22</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6.11亿</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2563,6 +4290,16 @@
           <t>华夏中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2021-12-07</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1.00亿</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2575,6 +4312,16 @@
           <t>天弘中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2022-01-04</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8.57亿</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2587,6 +4334,16 @@
           <t>兴银中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2022-01-26</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>7012.16万</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2599,6 +4356,16 @@
           <t>华安中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2022-07-12</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2867.73万</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2611,6 +4378,16 @@
           <t>太平中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2022-04-29</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3.02亿</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2623,6 +4400,16 @@
           <t>景顺长城中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2022-04-27</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>4686.89万</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2635,6 +4422,16 @@
           <t>中信建投中证1000A</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2022-06-28</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2.06亿</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2647,6 +4444,16 @@
           <t>国泰海通中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>11.75亿</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2659,6 +4466,16 @@
           <t>嘉实中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2022-12-06</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>5529.41万</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2671,6 +4488,16 @@
           <t>鹏华中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2022-12-26</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>20.08亿</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2683,6 +4510,16 @@
           <t>博时中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2023-04-13</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3.94亿</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2695,6 +4532,16 @@
           <t>工银瑞信中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2023-03-28</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>8.48亿</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2707,6 +4554,16 @@
           <t>国联安中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2022-12-05</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1.49亿</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2719,6 +4576,16 @@
           <t>申万菱信中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>3756.60万</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2731,6 +4598,16 @@
           <t>易方达中证1000指数量化增强A</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2023-04-25</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>5.59亿</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2743,6 +4620,16 @@
           <t>鑫元中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2022-11-28</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1.14亿</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2755,6 +4642,16 @@
           <t>农银中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1350.89万</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2767,6 +4664,16 @@
           <t>明亚中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2779,6 +4686,16 @@
           <t>博道中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2.88亿</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2791,6 +4708,16 @@
           <t>中金中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2023-03-14</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1.33亿</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2803,6 +4730,16 @@
           <t>国金中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2023-03-22</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2.01亿</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2815,6 +4752,16 @@
           <t>中欧中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2023-03-02</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2.64亿</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2827,6 +4774,16 @@
           <t>汇添富中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2023-05-19</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>14.72亿</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2839,6 +4796,16 @@
           <t>长信中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2023-04-20</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>3.87亿</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2851,6 +4818,16 @@
           <t>华泰紫金中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2023-06-08</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1698.95万</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2863,6 +4840,16 @@
           <t>西部利得中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2023-04-25</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2.08亿</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2875,6 +4862,16 @@
           <t>浙商中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1012.36万</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2887,6 +4884,16 @@
           <t>大成中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>7929.09万</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2899,6 +4906,16 @@
           <t>泰康中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1683.44万</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2911,6 +4928,16 @@
           <t>华泰柏瑞中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>8.38亿</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2923,6 +4950,16 @@
           <t>财通中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>453.93万</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2935,6 +4972,16 @@
           <t>财通资管中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1038.82万</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2947,6 +4994,16 @@
           <t>中银中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2023-12-12</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>3.02亿</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2959,6 +5016,16 @@
           <t>银华中证1000增强策略ETF</t>
         </is>
       </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2971,6 +5038,16 @@
           <t>国泰中证1000增强策略ETF</t>
         </is>
       </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2983,6 +5060,16 @@
           <t>招商中证1000增强策略ETF</t>
         </is>
       </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2995,6 +5082,16 @@
           <t>天弘中证1000增强策略ETF</t>
         </is>
       </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3007,6 +5104,16 @@
           <t>富国中证1000指数增强A</t>
         </is>
       </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2018-05-31</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>7.05亿</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3019,6 +5126,16 @@
           <t>鹏华中证1000增强策略ETF</t>
         </is>
       </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3031,6 +5148,16 @@
           <t>工银中证1000增强策略ETF</t>
         </is>
       </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3043,6 +5170,16 @@
           <t>华泰柏瑞中证1000增强策略ETF</t>
         </is>
       </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3053,6 +5190,16 @@
       <c r="B47" t="inlineStr">
         <is>
           <t>博时中证1000增强策略ETF</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -3067,7 +5214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3085,6 +5232,16 @@
           <t>基金简称</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>上市日期</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>规模</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3097,6 +5254,16 @@
           <t>民生加银中证全指指数增强A</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>670.64万</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3109,6 +5276,16 @@
           <t>博道中证全指指数增强A</t>
         </is>
       </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3121,6 +5298,16 @@
           <t>国金中证全指指数增强A</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6.98亿</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3133,6 +5320,16 @@
           <t>国泰海通中证全指指数增强A</t>
         </is>
       </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3145,6 +5342,16 @@
           <t>中金中证全指指数增强A</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1.70亿</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3157,6 +5364,16 @@
           <t>华泰保兴中证全指指数增强A</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1002.50万</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3169,6 +5386,16 @@
           <t>东方红中证全指指数增强A</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>5178.20万</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3181,6 +5408,16 @@
           <t>长江中证全指指数增强A</t>
         </is>
       </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3193,6 +5430,16 @@
           <t>上银中证全指指数增强A</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2237.80万</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3205,6 +5452,16 @@
           <t>华泰柏瑞中证全指指数增强A</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6147.03万</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3217,6 +5474,16 @@
           <t>兴全中证全指增强A</t>
         </is>
       </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3229,6 +5496,16 @@
           <t>浙商中证全指指数增强A</t>
         </is>
       </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3241,6 +5518,16 @@
           <t>兴业中证全指指数增强A</t>
         </is>
       </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3253,6 +5540,16 @@
           <t>宏利中证全指指数增强A</t>
         </is>
       </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3265,6 +5562,16 @@
           <t>东兴中证全指指数量化增强A</t>
         </is>
       </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3275,6 +5582,16 @@
       <c r="B17" t="inlineStr">
         <is>
           <t>太平中证全指指数增强A</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>

--- a/data/fund_whitelist.xlsx
+++ b/data/fund_whitelist.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" tabRatio="600" firstSheet="1" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="沪深300" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证全指" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -42,7 +42,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -53,12 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1A2E3D"/>
         <bgColor rgb="FF1A2E3D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -86,7 +80,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -457,6 +451,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="18.796875" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -497,9 +492,9 @@
           <t>2014-12-26</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>12.44亿</t>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -519,9 +514,9 @@
           <t>2013-10-29</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>28.94亿</t>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -541,9 +536,9 @@
           <t>2013-09-27</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>4.82亿</t>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -563,9 +558,9 @@
           <t>2014-05-19</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>7112.58万</t>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -585,9 +580,9 @@
           <t>2015-02-10</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>22.81亿</t>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -607,9 +602,9 @@
           <t>2015-03-24</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>3.46亿</t>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -629,9 +624,9 @@
           <t>2015-12-31</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1.13亿</t>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -651,9 +646,9 @@
           <t>2016-09-26</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>4.44亿</t>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -673,9 +668,9 @@
           <t>2016-07-22</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>10.69亿</t>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -695,9 +690,9 @@
           <t>2016-12-09</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>5.95亿</t>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -717,9 +712,9 @@
           <t>2017-01-25</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>9869.45万</t>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -739,9 +734,9 @@
           <t>2017-03-16</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>9.85亿</t>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -761,9 +756,9 @@
           <t>2017-02-10</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>4.28亿</t>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -783,9 +778,9 @@
           <t>2017-05-10</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>13.73亿</t>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -805,9 +800,9 @@
           <t>2018-02-11</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>8.38亿</t>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -827,9 +822,9 @@
           <t>2017-11-24</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>5.49亿</t>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -849,9 +844,9 @@
           <t>2017-12-26</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>9.13亿</t>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -871,9 +866,9 @@
           <t>2018-04-19</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>3.05亿</t>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -893,9 +888,9 @@
           <t>2019-12-18</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>7464.89万</t>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -915,9 +910,9 @@
           <t>2018-03-23</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>9.99亿</t>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -937,9 +932,9 @@
           <t>2019-01-30</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>1.46亿</t>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -959,9 +954,9 @@
           <t>2018-05-25</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>15.06亿</t>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -981,9 +976,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>4.90亿</t>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1003,9 +998,9 @@
           <t>2019-04-26</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>12.73亿</t>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1025,9 +1020,9 @@
           <t>2019-06-11</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>5.82亿</t>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1047,9 +1042,9 @@
           <t>2019-08-29</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2.14亿</t>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1069,9 +1064,9 @@
           <t>2020-04-01</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2.87亿</t>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1091,9 +1086,9 @@
           <t>2019-12-27</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>7.09亿</t>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1113,9 +1108,9 @@
           <t>2020-04-23</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2.41亿</t>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1135,9 +1130,9 @@
           <t>2020-12-30</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>20.74亿</t>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1157,9 +1152,9 @@
           <t>2021-01-20</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>30.42亿</t>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1179,9 +1174,9 @@
           <t>2020-12-30</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>4036.62万</t>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1201,9 +1196,9 @@
           <t>2021-02-23</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>8120.31万</t>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1223,9 +1218,9 @@
           <t>2021-06-02</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>6496.02万</t>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1245,9 +1240,9 @@
           <t>2021-07-05</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2523.15万</t>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1267,9 +1262,9 @@
           <t>2021-07-23</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2688.43万</t>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1289,9 +1284,9 @@
           <t>2025-06-17</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>1280.40万</t>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1311,9 +1306,9 @@
           <t>2022-07-27</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>1.29亿</t>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1333,9 +1328,9 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>3.74亿</t>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1355,9 +1350,9 @@
           <t>2022-11-08</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2785.47万</t>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1377,9 +1372,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>11.93亿</t>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1399,9 +1394,9 @@
           <t>2023-12-18</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>1.51亿</t>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1421,9 +1416,9 @@
           <t>2024-01-23</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2.90亿</t>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1443,9 +1438,9 @@
           <t>2024-11-29</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>7.56亿</t>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1465,9 +1460,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>1519.04万</t>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1487,9 +1482,9 @@
           <t>2024-11-26</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2781.16万</t>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1509,9 +1504,9 @@
           <t>2024-11-26</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2.42亿</t>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1531,9 +1526,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1553,9 +1548,9 @@
           <t>2025-01-21</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>4.10亿</t>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1575,9 +1570,9 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>3143.65万</t>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1597,9 +1592,9 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>4805.47万</t>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1619,9 +1614,9 @@
           <t>2025-05-16</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2345.43万</t>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1641,9 +1636,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2234.59万</t>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1663,9 +1658,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1685,9 +1680,9 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2647.94万</t>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1707,9 +1702,9 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>1959.58万</t>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1729,9 +1724,9 @@
           <t>2025-09-02</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>3375.37万</t>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1751,9 +1746,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>737.52万</t>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1773,9 +1768,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>1.66亿</t>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1795,9 +1790,9 @@
           <t>2025-12-30</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>9.34亿</t>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1817,9 +1812,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>1372.07万</t>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1839,9 +1834,9 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>1363.58万</t>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1861,9 +1856,9 @@
           <t>2025-11-21</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2.31亿</t>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1883,9 +1878,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1905,9 +1900,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1927,9 +1922,9 @@
           <t>2009-12-16</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>46.17亿</t>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1949,9 +1944,9 @@
           <t>2012-07-05</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>9.35亿</t>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1971,9 +1966,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -1993,9 +1988,9 @@
           <t>2010-04-23</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>5.39亿</t>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2015,9 +2010,9 @@
           <t>2010-11-02</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>39.43亿</t>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2037,9 +2032,9 @@
           <t>2011-05-06</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>2.89亿</t>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2059,9 +2054,9 @@
           <t>2012-05-07</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>1.54亿</t>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2081,9 +2076,9 @@
           <t>2013-07-26</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>9469.08万</t>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2103,9 +2098,9 @@
           <t>2004-05-21</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>7.98亿</t>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2125,9 +2120,9 @@
           <t>2004-11-29</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>8.07亿</t>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2147,9 +2142,9 @@
           <t>2011-04-07</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>3.53亿</t>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2169,9 +2164,9 @@
           <t>2009-09-03</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>2.32亿</t>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2191,9 +2186,9 @@
           <t>2010-12-10</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>2.36亿</t>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2213,9 +2208,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2235,9 +2230,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2257,9 +2252,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D82" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2279,9 +2274,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2301,9 +2296,9 @@
           <t>2017-03-21</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>2.14亿</t>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2323,6 +2318,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="11.1328125" bestFit="1" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2363,9 +2359,9 @@
           <t>2014-01-27</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>33.32亿</t>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2385,9 +2381,9 @@
           <t>2015-02-16</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>13.03亿</t>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2407,9 +2403,9 @@
           <t>2015-06-09</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2758.73万</t>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2429,9 +2425,9 @@
           <t>2015-06-30</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>19.13亿</t>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2451,9 +2447,9 @@
           <t>2016-05-11</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1.32亿</t>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2473,9 +2469,9 @@
           <t>2015-12-31</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1.80亿</t>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2495,9 +2491,9 @@
           <t>2016-04-21</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1.33亿</t>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2517,9 +2513,9 @@
           <t>2016-11-23</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>4.08亿</t>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2539,9 +2535,9 @@
           <t>2016-07-22</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>8.87亿</t>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2561,9 +2557,9 @@
           <t>2017-08-01</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>8243.26万</t>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2583,9 +2579,9 @@
           <t>2017-01-10</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>14.92亿</t>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2605,9 +2601,9 @@
           <t>2017-05-17</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>6.24亿</t>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2627,9 +2623,9 @@
           <t>2017-08-30</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2.44亿</t>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2649,9 +2645,9 @@
           <t>2017-09-26</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2.47亿</t>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2671,9 +2667,9 @@
           <t>2018-04-19</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>3092.56万</t>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2693,9 +2689,9 @@
           <t>2018-11-29</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>1156.65万</t>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2715,9 +2711,9 @@
           <t>2018-08-01</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>9.74亿</t>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2737,9 +2733,9 @@
           <t>2018-08-13</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>8.38亿</t>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2759,9 +2755,9 @@
           <t>2020-05-09</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>9843.42万</t>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2781,9 +2777,9 @@
           <t>2019-01-03</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>14.95亿</t>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2803,9 +2799,9 @@
           <t>2019-03-25</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>4.18亿</t>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2825,9 +2821,9 @@
           <t>2019-05-23</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>6.47亿</t>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2847,9 +2843,9 @@
           <t>2019-11-19</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>7830.15万</t>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2869,9 +2865,9 @@
           <t>2020-03-25</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>38.06亿</t>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2891,9 +2887,9 @@
           <t>2020-01-20</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>7786.00万</t>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2913,9 +2909,9 @@
           <t>2020-05-27</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>1390.64万</t>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2935,9 +2931,9 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>1.85亿</t>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2957,9 +2953,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>3629.30万</t>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -2979,9 +2975,9 @@
           <t>2020-12-23</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>4.78亿</t>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3001,9 +2997,9 @@
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>1897.09万</t>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3023,9 +3019,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3045,9 +3041,9 @@
           <t>2021-03-01</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2701.93万</t>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3067,9 +3063,9 @@
           <t>2021-06-15</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>4.72亿</t>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3089,9 +3085,9 @@
           <t>2021-09-16</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>4901.87万</t>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3111,9 +3107,9 @@
           <t>2021-08-10</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>3505.66万</t>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3133,9 +3129,9 @@
           <t>2021-08-11</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>9.12亿</t>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3155,9 +3151,9 @@
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>1.04亿</t>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3177,9 +3173,9 @@
           <t>2021-12-01</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>9277.21万</t>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3199,9 +3195,9 @@
           <t>2021-12-14</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>8935.54万</t>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3221,9 +3217,9 @@
           <t>2021-12-15</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>24.84亿</t>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3243,9 +3239,9 @@
           <t>2022-04-27</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>3.20亿</t>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3265,9 +3261,9 @@
           <t>2022-01-11</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>10.23亿</t>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3287,9 +3283,9 @@
           <t>2022-05-24</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>4339.94万</t>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3309,9 +3305,9 @@
           <t>2022-05-06</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>18.60亿</t>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3331,9 +3327,9 @@
           <t>2022-06-07</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>1.55亿</t>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3353,9 +3349,9 @@
           <t>2022-12-23</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>1.09亿</t>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3375,9 +3371,9 @@
           <t>2022-10-25</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>559.34万</t>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3397,9 +3393,9 @@
           <t>2023-02-22</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>3486.24万</t>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3419,9 +3415,9 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2161.54万</t>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3441,9 +3437,9 @@
           <t>2023-07-13</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2935.08万</t>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3463,9 +3459,9 @@
           <t>2023-12-26</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2027.83万</t>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3485,9 +3481,9 @@
           <t>2024-08-13</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>1.13亿</t>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3507,9 +3503,9 @@
           <t>2024-07-19</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>1905.22万</t>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3529,9 +3525,9 @@
           <t>2024-07-09</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>3421.12万</t>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3551,9 +3547,9 @@
           <t>2024-06-21</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>7240.92万</t>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3573,9 +3569,9 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2143.25万</t>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3595,9 +3591,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3617,9 +3613,9 @@
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>1.10亿</t>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3639,9 +3635,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3661,9 +3657,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>6399.46万</t>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3683,9 +3679,9 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>7658.44万</t>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3705,9 +3701,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3727,9 +3723,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>3856.85万</t>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3749,9 +3745,9 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>4.35亿</t>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3771,9 +3767,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3793,9 +3789,9 @@
           <t>2025-11-25</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>3404.98万</t>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3815,9 +3811,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3837,9 +3833,9 @@
           <t>2025-12-19</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>8088.65万</t>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3859,9 +3855,9 @@
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>5.78亿</t>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3881,9 +3877,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3903,9 +3899,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3925,9 +3921,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3947,9 +3943,9 @@
           <t>2011-10-12</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>39.47亿</t>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3969,9 +3965,9 @@
           <t>2011-12-01</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>1.75亿</t>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -3991,9 +3987,9 @@
           <t>2015-04-15</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>10.72亿</t>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4013,9 +4009,9 @@
           <t>2012-05-25</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>2978.59万</t>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4035,9 +4031,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4057,9 +4053,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4079,9 +4075,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4101,9 +4097,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4123,9 +4119,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D82" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4145,9 +4141,9 @@
           <t>2011-11-22</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>5731.22万</t>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4167,6 +4163,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="11.1328125" bestFit="1" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4207,9 +4204,9 @@
           <t>2016-12-22</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>3575.34万</t>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4229,9 +4226,9 @@
           <t>2017-03-03</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>10.48亿</t>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4251,9 +4248,9 @@
           <t>2018-01-30</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>8.49亿</t>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4273,9 +4270,9 @@
           <t>2018-11-22</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>6.11亿</t>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4295,9 +4292,9 @@
           <t>2021-12-07</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1.00亿</t>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4317,9 +4314,9 @@
           <t>2022-01-04</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>8.57亿</t>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4339,9 +4336,9 @@
           <t>2022-01-26</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>7012.16万</t>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4361,9 +4358,9 @@
           <t>2022-07-12</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2867.73万</t>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4383,9 +4380,9 @@
           <t>2022-04-29</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>3.02亿</t>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4405,9 +4402,9 @@
           <t>2022-04-27</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>4686.89万</t>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4427,9 +4424,9 @@
           <t>2022-06-28</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2.06亿</t>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4449,9 +4446,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>11.75亿</t>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4471,9 +4468,9 @@
           <t>2022-12-06</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>5529.41万</t>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4493,9 +4490,9 @@
           <t>2022-12-26</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>20.08亿</t>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4515,9 +4512,9 @@
           <t>2023-04-13</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>3.94亿</t>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4537,9 +4534,9 @@
           <t>2023-03-28</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>8.48亿</t>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4559,9 +4556,9 @@
           <t>2022-12-05</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>1.49亿</t>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4581,9 +4578,9 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>3756.60万</t>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4603,9 +4600,9 @@
           <t>2023-04-25</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>5.59亿</t>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4625,9 +4622,9 @@
           <t>2022-11-28</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>1.14亿</t>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4647,9 +4644,9 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>1350.89万</t>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4669,9 +4666,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4691,9 +4688,9 @@
           <t>2023-08-25</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2.88亿</t>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4713,9 +4710,9 @@
           <t>2023-03-14</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>1.33亿</t>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4735,9 +4732,9 @@
           <t>2023-03-22</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2.01亿</t>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4757,9 +4754,9 @@
           <t>2023-03-02</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2.64亿</t>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4779,9 +4776,9 @@
           <t>2023-05-19</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>14.72亿</t>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4801,9 +4798,9 @@
           <t>2023-04-20</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>3.87亿</t>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4823,9 +4820,9 @@
           <t>2023-06-08</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>1698.95万</t>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4845,9 +4842,9 @@
           <t>2023-04-25</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2.08亿</t>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4867,9 +4864,9 @@
           <t>2023-09-26</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>1012.36万</t>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4889,9 +4886,9 @@
           <t>2023-08-01</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>7929.09万</t>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4911,9 +4908,9 @@
           <t>2023-10-26</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>1683.44万</t>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4933,9 +4930,9 @@
           <t>2023-09-19</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>8.38亿</t>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4955,9 +4952,9 @@
           <t>2023-11-07</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>453.93万</t>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4977,9 +4974,9 @@
           <t>2024-04-29</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>1038.82万</t>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -4999,17 +4996,15 @@
           <t>2023-12-12</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>3.02亿</t>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>159677</t>
-        </is>
+      <c r="A39" t="n">
+        <v>159677</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -5021,9 +5016,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -5043,9 +5038,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -5065,9 +5060,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -5087,9 +5082,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -5109,9 +5104,9 @@
           <t>2018-05-31</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>7.05亿</t>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -5131,9 +5126,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -5153,9 +5148,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -5175,9 +5170,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -5197,9 +5192,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -5219,6 +5214,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="11.1328125" bestFit="1" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5259,9 +5255,9 @@
           <t>2025-03-20</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>670.64万</t>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -5281,9 +5277,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -5303,9 +5299,9 @@
           <t>2025-09-16</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>6.98亿</t>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -5325,9 +5321,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -5347,9 +5343,9 @@
           <t>2025-11-12</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1.70亿</t>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -5369,9 +5365,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1002.50万</t>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -5391,9 +5387,9 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>5178.20万</t>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -5413,9 +5409,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -5435,9 +5431,9 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2237.80万</t>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -5457,9 +5453,9 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>6147.03万</t>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -5479,9 +5475,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -5501,9 +5497,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -5523,9 +5519,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -5545,9 +5541,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -5567,9 +5563,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>
@@ -5589,9 +5585,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
         </is>
       </c>
     </row>

--- a/data/fund_whitelist.xlsx
+++ b/data/fund_whitelist.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" tabRatio="600" firstSheet="1" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="沪深300" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证全指" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -42,7 +42,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +53,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1A2E3D"/>
         <bgColor rgb="FF1A2E3D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -80,7 +86,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -451,7 +457,6 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="18.796875" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -492,9 +497,9 @@
           <t>2014-12-26</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>12.44亿</t>
         </is>
       </c>
     </row>
@@ -514,9 +519,9 @@
           <t>2013-10-29</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>28.94亿</t>
         </is>
       </c>
     </row>
@@ -536,9 +541,9 @@
           <t>2013-09-27</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>4.82亿</t>
         </is>
       </c>
     </row>
@@ -558,9 +563,9 @@
           <t>2014-05-19</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7112.58万</t>
         </is>
       </c>
     </row>
@@ -580,9 +585,9 @@
           <t>2015-02-10</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>22.81亿</t>
         </is>
       </c>
     </row>
@@ -602,9 +607,9 @@
           <t>2015-03-24</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3.46亿</t>
         </is>
       </c>
     </row>
@@ -624,9 +629,9 @@
           <t>2015-12-31</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1.13亿</t>
         </is>
       </c>
     </row>
@@ -646,9 +651,9 @@
           <t>2016-09-26</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4.44亿</t>
         </is>
       </c>
     </row>
@@ -668,9 +673,9 @@
           <t>2016-07-22</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>10.69亿</t>
         </is>
       </c>
     </row>
@@ -690,9 +695,9 @@
           <t>2016-12-09</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>5.95亿</t>
         </is>
       </c>
     </row>
@@ -712,9 +717,9 @@
           <t>2017-01-25</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>9869.45万</t>
         </is>
       </c>
     </row>
@@ -734,9 +739,9 @@
           <t>2017-03-16</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>9.85亿</t>
         </is>
       </c>
     </row>
@@ -756,9 +761,9 @@
           <t>2017-02-10</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4.28亿</t>
         </is>
       </c>
     </row>
@@ -778,9 +783,9 @@
           <t>2017-05-10</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>13.73亿</t>
         </is>
       </c>
     </row>
@@ -800,9 +805,9 @@
           <t>2018-02-11</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8.38亿</t>
         </is>
       </c>
     </row>
@@ -822,9 +827,9 @@
           <t>2017-11-24</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>5.49亿</t>
         </is>
       </c>
     </row>
@@ -844,9 +849,9 @@
           <t>2017-12-26</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>9.13亿</t>
         </is>
       </c>
     </row>
@@ -866,9 +871,9 @@
           <t>2018-04-19</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>3.05亿</t>
         </is>
       </c>
     </row>
@@ -888,9 +893,9 @@
           <t>2019-12-18</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>7464.89万</t>
         </is>
       </c>
     </row>
@@ -910,9 +915,9 @@
           <t>2018-03-23</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>9.99亿</t>
         </is>
       </c>
     </row>
@@ -932,9 +937,9 @@
           <t>2019-01-30</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1.46亿</t>
         </is>
       </c>
     </row>
@@ -954,9 +959,9 @@
           <t>2018-05-25</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>15.06亿</t>
         </is>
       </c>
     </row>
@@ -976,9 +981,9 @@
           <t>2018-06-29</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>4.90亿</t>
         </is>
       </c>
     </row>
@@ -998,9 +1003,9 @@
           <t>2019-04-26</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>12.73亿</t>
         </is>
       </c>
     </row>
@@ -1020,9 +1025,9 @@
           <t>2019-06-11</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>5.82亿</t>
         </is>
       </c>
     </row>
@@ -1042,9 +1047,9 @@
           <t>2019-08-29</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2.14亿</t>
         </is>
       </c>
     </row>
@@ -1064,9 +1069,9 @@
           <t>2020-04-01</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2.87亿</t>
         </is>
       </c>
     </row>
@@ -1086,9 +1091,9 @@
           <t>2019-12-27</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>7.09亿</t>
         </is>
       </c>
     </row>
@@ -1108,9 +1113,9 @@
           <t>2020-04-23</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2.41亿</t>
         </is>
       </c>
     </row>
@@ -1130,9 +1135,9 @@
           <t>2020-12-30</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>20.74亿</t>
         </is>
       </c>
     </row>
@@ -1152,9 +1157,9 @@
           <t>2021-01-20</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>30.42亿</t>
         </is>
       </c>
     </row>
@@ -1174,9 +1179,9 @@
           <t>2020-12-30</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>4036.62万</t>
         </is>
       </c>
     </row>
@@ -1196,9 +1201,9 @@
           <t>2021-02-23</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>8120.31万</t>
         </is>
       </c>
     </row>
@@ -1218,9 +1223,9 @@
           <t>2021-06-02</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>6496.02万</t>
         </is>
       </c>
     </row>
@@ -1240,9 +1245,9 @@
           <t>2021-07-05</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2523.15万</t>
         </is>
       </c>
     </row>
@@ -1262,9 +1267,9 @@
           <t>2021-07-23</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2688.43万</t>
         </is>
       </c>
     </row>
@@ -1284,9 +1289,9 @@
           <t>2025-06-17</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1280.40万</t>
         </is>
       </c>
     </row>
@@ -1306,9 +1311,9 @@
           <t>2022-07-27</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1.29亿</t>
         </is>
       </c>
     </row>
@@ -1328,9 +1333,9 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>3.74亿</t>
         </is>
       </c>
     </row>
@@ -1350,9 +1355,9 @@
           <t>2022-11-08</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2785.47万</t>
         </is>
       </c>
     </row>
@@ -1372,9 +1377,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>11.93亿</t>
         </is>
       </c>
     </row>
@@ -1394,9 +1399,9 @@
           <t>2023-12-18</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1.51亿</t>
         </is>
       </c>
     </row>
@@ -1416,9 +1421,9 @@
           <t>2024-01-23</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2.90亿</t>
         </is>
       </c>
     </row>
@@ -1438,9 +1443,9 @@
           <t>2024-11-29</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>7.56亿</t>
         </is>
       </c>
     </row>
@@ -1460,9 +1465,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1519.04万</t>
         </is>
       </c>
     </row>
@@ -1482,9 +1487,9 @@
           <t>2024-11-26</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2781.16万</t>
         </is>
       </c>
     </row>
@@ -1504,9 +1509,9 @@
           <t>2024-11-26</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2.42亿</t>
         </is>
       </c>
     </row>
@@ -1526,9 +1531,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -1548,9 +1553,9 @@
           <t>2025-01-21</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>4.10亿</t>
         </is>
       </c>
     </row>
@@ -1570,9 +1575,9 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>3143.65万</t>
         </is>
       </c>
     </row>
@@ -1592,9 +1597,9 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>4805.47万</t>
         </is>
       </c>
     </row>
@@ -1614,9 +1619,9 @@
           <t>2025-05-16</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2345.43万</t>
         </is>
       </c>
     </row>
@@ -1636,9 +1641,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2234.59万</t>
         </is>
       </c>
     </row>
@@ -1658,9 +1663,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -1680,9 +1685,9 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2647.94万</t>
         </is>
       </c>
     </row>
@@ -1702,9 +1707,9 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1959.58万</t>
         </is>
       </c>
     </row>
@@ -1724,9 +1729,9 @@
           <t>2025-09-02</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>3375.37万</t>
         </is>
       </c>
     </row>
@@ -1746,9 +1751,9 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>737.52万</t>
         </is>
       </c>
     </row>
@@ -1768,9 +1773,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1.66亿</t>
         </is>
       </c>
     </row>
@@ -1790,9 +1795,9 @@
           <t>2025-12-30</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>9.34亿</t>
         </is>
       </c>
     </row>
@@ -1812,9 +1817,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1372.07万</t>
         </is>
       </c>
     </row>
@@ -1834,9 +1839,9 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1363.58万</t>
         </is>
       </c>
     </row>
@@ -1856,9 +1861,9 @@
           <t>2025-11-21</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2.31亿</t>
         </is>
       </c>
     </row>
@@ -1878,9 +1883,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -1900,9 +1905,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -1922,9 +1927,9 @@
           <t>2009-12-16</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>46.17亿</t>
         </is>
       </c>
     </row>
@@ -1944,9 +1949,9 @@
           <t>2012-07-05</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>9.35亿</t>
         </is>
       </c>
     </row>
@@ -1966,9 +1971,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -1988,9 +1993,9 @@
           <t>2010-04-23</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>5.39亿</t>
         </is>
       </c>
     </row>
@@ -2010,9 +2015,9 @@
           <t>2010-11-02</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>39.43亿</t>
         </is>
       </c>
     </row>
@@ -2032,9 +2037,9 @@
           <t>2011-05-06</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2.89亿</t>
         </is>
       </c>
     </row>
@@ -2054,9 +2059,9 @@
           <t>2012-05-07</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1.54亿</t>
         </is>
       </c>
     </row>
@@ -2076,9 +2081,9 @@
           <t>2013-07-26</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>9469.08万</t>
         </is>
       </c>
     </row>
@@ -2098,9 +2103,9 @@
           <t>2004-05-21</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>7.98亿</t>
         </is>
       </c>
     </row>
@@ -2120,9 +2125,9 @@
           <t>2004-11-29</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>8.07亿</t>
         </is>
       </c>
     </row>
@@ -2142,9 +2147,9 @@
           <t>2011-04-07</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>3.53亿</t>
         </is>
       </c>
     </row>
@@ -2164,9 +2169,9 @@
           <t>2009-09-03</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2.32亿</t>
         </is>
       </c>
     </row>
@@ -2186,9 +2191,9 @@
           <t>2010-12-10</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2.36亿</t>
         </is>
       </c>
     </row>
@@ -2208,9 +2213,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -2230,9 +2235,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -2252,9 +2257,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -2274,9 +2279,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -2296,9 +2301,9 @@
           <t>2017-03-21</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2.14亿</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2323,6 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="11.1328125" bestFit="1" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2359,9 +2363,9 @@
           <t>2014-01-27</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>33.32亿</t>
         </is>
       </c>
     </row>
@@ -2381,9 +2385,9 @@
           <t>2015-02-16</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>13.03亿</t>
         </is>
       </c>
     </row>
@@ -2403,9 +2407,9 @@
           <t>2015-06-09</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2758.73万</t>
         </is>
       </c>
     </row>
@@ -2425,9 +2429,9 @@
           <t>2015-06-30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>19.13亿</t>
         </is>
       </c>
     </row>
@@ -2447,9 +2451,9 @@
           <t>2016-05-11</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1.32亿</t>
         </is>
       </c>
     </row>
@@ -2469,9 +2473,9 @@
           <t>2015-12-31</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1.80亿</t>
         </is>
       </c>
     </row>
@@ -2491,9 +2495,9 @@
           <t>2016-04-21</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1.33亿</t>
         </is>
       </c>
     </row>
@@ -2513,9 +2517,9 @@
           <t>2016-11-23</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4.08亿</t>
         </is>
       </c>
     </row>
@@ -2535,9 +2539,9 @@
           <t>2016-07-22</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8.87亿</t>
         </is>
       </c>
     </row>
@@ -2557,9 +2561,9 @@
           <t>2017-08-01</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8243.26万</t>
         </is>
       </c>
     </row>
@@ -2579,9 +2583,9 @@
           <t>2017-01-10</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>14.92亿</t>
         </is>
       </c>
     </row>
@@ -2601,9 +2605,9 @@
           <t>2017-05-17</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>6.24亿</t>
         </is>
       </c>
     </row>
@@ -2623,9 +2627,9 @@
           <t>2017-08-30</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2.44亿</t>
         </is>
       </c>
     </row>
@@ -2645,9 +2649,9 @@
           <t>2017-09-26</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2.47亿</t>
         </is>
       </c>
     </row>
@@ -2667,9 +2671,9 @@
           <t>2018-04-19</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3092.56万</t>
         </is>
       </c>
     </row>
@@ -2689,9 +2693,9 @@
           <t>2018-11-29</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1156.65万</t>
         </is>
       </c>
     </row>
@@ -2711,9 +2715,9 @@
           <t>2018-08-01</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>9.74亿</t>
         </is>
       </c>
     </row>
@@ -2733,9 +2737,9 @@
           <t>2018-08-13</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>8.38亿</t>
         </is>
       </c>
     </row>
@@ -2755,9 +2759,9 @@
           <t>2020-05-09</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>9843.42万</t>
         </is>
       </c>
     </row>
@@ -2777,9 +2781,9 @@
           <t>2019-01-03</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>14.95亿</t>
         </is>
       </c>
     </row>
@@ -2799,9 +2803,9 @@
           <t>2019-03-25</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>4.18亿</t>
         </is>
       </c>
     </row>
@@ -2821,9 +2825,9 @@
           <t>2019-05-23</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>6.47亿</t>
         </is>
       </c>
     </row>
@@ -2843,9 +2847,9 @@
           <t>2019-11-19</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>7830.15万</t>
         </is>
       </c>
     </row>
@@ -2865,9 +2869,9 @@
           <t>2020-03-25</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>38.06亿</t>
         </is>
       </c>
     </row>
@@ -2887,9 +2891,9 @@
           <t>2020-01-20</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>7786.00万</t>
         </is>
       </c>
     </row>
@@ -2909,9 +2913,9 @@
           <t>2020-05-27</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1390.64万</t>
         </is>
       </c>
     </row>
@@ -2931,9 +2935,9 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1.85亿</t>
         </is>
       </c>
     </row>
@@ -2953,9 +2957,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>3629.30万</t>
         </is>
       </c>
     </row>
@@ -2975,9 +2979,9 @@
           <t>2020-12-23</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>4.78亿</t>
         </is>
       </c>
     </row>
@@ -2997,9 +3001,9 @@
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1897.09万</t>
         </is>
       </c>
     </row>
@@ -3019,9 +3023,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -3041,9 +3045,9 @@
           <t>2021-03-01</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2701.93万</t>
         </is>
       </c>
     </row>
@@ -3063,9 +3067,9 @@
           <t>2021-06-15</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>4.72亿</t>
         </is>
       </c>
     </row>
@@ -3085,9 +3089,9 @@
           <t>2021-09-16</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>4901.87万</t>
         </is>
       </c>
     </row>
@@ -3107,9 +3111,9 @@
           <t>2021-08-10</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>3505.66万</t>
         </is>
       </c>
     </row>
@@ -3129,9 +3133,9 @@
           <t>2021-08-11</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>9.12亿</t>
         </is>
       </c>
     </row>
@@ -3151,9 +3155,9 @@
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1.04亿</t>
         </is>
       </c>
     </row>
@@ -3173,9 +3177,9 @@
           <t>2021-12-01</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>9277.21万</t>
         </is>
       </c>
     </row>
@@ -3195,9 +3199,9 @@
           <t>2021-12-14</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>8935.54万</t>
         </is>
       </c>
     </row>
@@ -3217,9 +3221,9 @@
           <t>2021-12-15</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>24.84亿</t>
         </is>
       </c>
     </row>
@@ -3239,9 +3243,9 @@
           <t>2022-04-27</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>3.20亿</t>
         </is>
       </c>
     </row>
@@ -3261,9 +3265,9 @@
           <t>2022-01-11</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>10.23亿</t>
         </is>
       </c>
     </row>
@@ -3283,9 +3287,9 @@
           <t>2022-05-24</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>4339.94万</t>
         </is>
       </c>
     </row>
@@ -3305,9 +3309,9 @@
           <t>2022-05-06</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>18.60亿</t>
         </is>
       </c>
     </row>
@@ -3327,9 +3331,9 @@
           <t>2022-06-07</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1.55亿</t>
         </is>
       </c>
     </row>
@@ -3349,9 +3353,9 @@
           <t>2022-12-23</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1.09亿</t>
         </is>
       </c>
     </row>
@@ -3371,9 +3375,9 @@
           <t>2022-10-25</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>559.34万</t>
         </is>
       </c>
     </row>
@@ -3393,9 +3397,9 @@
           <t>2023-02-22</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>3486.24万</t>
         </is>
       </c>
     </row>
@@ -3415,9 +3419,9 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2161.54万</t>
         </is>
       </c>
     </row>
@@ -3437,9 +3441,9 @@
           <t>2023-07-13</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2935.08万</t>
         </is>
       </c>
     </row>
@@ -3459,9 +3463,9 @@
           <t>2023-12-26</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2027.83万</t>
         </is>
       </c>
     </row>
@@ -3481,9 +3485,9 @@
           <t>2024-08-13</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1.13亿</t>
         </is>
       </c>
     </row>
@@ -3503,9 +3507,9 @@
           <t>2024-07-19</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1905.22万</t>
         </is>
       </c>
     </row>
@@ -3525,9 +3529,9 @@
           <t>2024-07-09</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3421.12万</t>
         </is>
       </c>
     </row>
@@ -3547,9 +3551,9 @@
           <t>2024-06-21</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>7240.92万</t>
         </is>
       </c>
     </row>
@@ -3569,9 +3573,9 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2143.25万</t>
         </is>
       </c>
     </row>
@@ -3591,9 +3595,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -3613,9 +3617,9 @@
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1.10亿</t>
         </is>
       </c>
     </row>
@@ -3635,9 +3639,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -3657,9 +3661,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>6399.46万</t>
         </is>
       </c>
     </row>
@@ -3679,9 +3683,9 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>7658.44万</t>
         </is>
       </c>
     </row>
@@ -3701,9 +3705,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -3723,9 +3727,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>3856.85万</t>
         </is>
       </c>
     </row>
@@ -3745,9 +3749,9 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>4.35亿</t>
         </is>
       </c>
     </row>
@@ -3767,9 +3771,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -3789,9 +3793,9 @@
           <t>2025-11-25</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>3404.98万</t>
         </is>
       </c>
     </row>
@@ -3811,9 +3815,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -3833,9 +3837,9 @@
           <t>2025-12-19</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>8088.65万</t>
         </is>
       </c>
     </row>
@@ -3855,9 +3859,9 @@
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>5.78亿</t>
         </is>
       </c>
     </row>
@@ -3877,9 +3881,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -3899,9 +3903,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -3921,9 +3925,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -3943,9 +3947,9 @@
           <t>2011-10-12</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>39.47亿</t>
         </is>
       </c>
     </row>
@@ -3965,9 +3969,9 @@
           <t>2011-12-01</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1.75亿</t>
         </is>
       </c>
     </row>
@@ -3987,9 +3991,9 @@
           <t>2015-04-15</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>10.72亿</t>
         </is>
       </c>
     </row>
@@ -4009,9 +4013,9 @@
           <t>2012-05-25</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2978.59万</t>
         </is>
       </c>
     </row>
@@ -4031,9 +4035,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -4053,9 +4057,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -4075,9 +4079,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -4097,9 +4101,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -4119,9 +4123,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -4141,9 +4145,9 @@
           <t>2011-11-22</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>5731.22万</t>
         </is>
       </c>
     </row>
@@ -4163,7 +4167,6 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="11.1328125" bestFit="1" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4204,9 +4207,9 @@
           <t>2016-12-22</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3575.34万</t>
         </is>
       </c>
     </row>
@@ -4226,9 +4229,9 @@
           <t>2017-03-03</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>10.48亿</t>
         </is>
       </c>
     </row>
@@ -4248,9 +4251,9 @@
           <t>2018-01-30</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8.49亿</t>
         </is>
       </c>
     </row>
@@ -4270,9 +4273,9 @@
           <t>2018-11-22</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6.11亿</t>
         </is>
       </c>
     </row>
@@ -4292,9 +4295,9 @@
           <t>2021-12-07</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1.00亿</t>
         </is>
       </c>
     </row>
@@ -4314,9 +4317,9 @@
           <t>2022-01-04</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8.57亿</t>
         </is>
       </c>
     </row>
@@ -4336,9 +4339,9 @@
           <t>2022-01-26</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>7012.16万</t>
         </is>
       </c>
     </row>
@@ -4358,9 +4361,9 @@
           <t>2022-07-12</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2867.73万</t>
         </is>
       </c>
     </row>
@@ -4380,9 +4383,9 @@
           <t>2022-04-29</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3.02亿</t>
         </is>
       </c>
     </row>
@@ -4402,9 +4405,9 @@
           <t>2022-04-27</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>4686.89万</t>
         </is>
       </c>
     </row>
@@ -4424,9 +4427,9 @@
           <t>2022-06-28</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2.06亿</t>
         </is>
       </c>
     </row>
@@ -4446,9 +4449,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>11.75亿</t>
         </is>
       </c>
     </row>
@@ -4468,9 +4471,9 @@
           <t>2022-12-06</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>5529.41万</t>
         </is>
       </c>
     </row>
@@ -4490,9 +4493,9 @@
           <t>2022-12-26</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>20.08亿</t>
         </is>
       </c>
     </row>
@@ -4512,9 +4515,9 @@
           <t>2023-04-13</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3.94亿</t>
         </is>
       </c>
     </row>
@@ -4534,9 +4537,9 @@
           <t>2023-03-28</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>8.48亿</t>
         </is>
       </c>
     </row>
@@ -4556,9 +4559,9 @@
           <t>2022-12-05</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1.49亿</t>
         </is>
       </c>
     </row>
@@ -4578,9 +4581,9 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>3756.60万</t>
         </is>
       </c>
     </row>
@@ -4600,9 +4603,9 @@
           <t>2023-04-25</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>5.59亿</t>
         </is>
       </c>
     </row>
@@ -4622,9 +4625,9 @@
           <t>2022-11-28</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1.14亿</t>
         </is>
       </c>
     </row>
@@ -4644,9 +4647,9 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1350.89万</t>
         </is>
       </c>
     </row>
@@ -4666,9 +4669,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -4688,9 +4691,9 @@
           <t>2023-08-25</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2.88亿</t>
         </is>
       </c>
     </row>
@@ -4710,9 +4713,9 @@
           <t>2023-03-14</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1.33亿</t>
         </is>
       </c>
     </row>
@@ -4732,9 +4735,9 @@
           <t>2023-03-22</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2.01亿</t>
         </is>
       </c>
     </row>
@@ -4754,9 +4757,9 @@
           <t>2023-03-02</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2.64亿</t>
         </is>
       </c>
     </row>
@@ -4776,9 +4779,9 @@
           <t>2023-05-19</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>14.72亿</t>
         </is>
       </c>
     </row>
@@ -4798,9 +4801,9 @@
           <t>2023-04-20</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>3.87亿</t>
         </is>
       </c>
     </row>
@@ -4820,9 +4823,9 @@
           <t>2023-06-08</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1698.95万</t>
         </is>
       </c>
     </row>
@@ -4842,9 +4845,9 @@
           <t>2023-04-25</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2.08亿</t>
         </is>
       </c>
     </row>
@@ -4864,9 +4867,9 @@
           <t>2023-09-26</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1012.36万</t>
         </is>
       </c>
     </row>
@@ -4886,9 +4889,9 @@
           <t>2023-08-01</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>7929.09万</t>
         </is>
       </c>
     </row>
@@ -4908,9 +4911,9 @@
           <t>2023-10-26</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1683.44万</t>
         </is>
       </c>
     </row>
@@ -4930,9 +4933,9 @@
           <t>2023-09-19</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>8.38亿</t>
         </is>
       </c>
     </row>
@@ -4952,9 +4955,9 @@
           <t>2023-11-07</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>453.93万</t>
         </is>
       </c>
     </row>
@@ -4974,9 +4977,9 @@
           <t>2024-04-29</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1038.82万</t>
         </is>
       </c>
     </row>
@@ -4996,15 +4999,17 @@
           <t>2023-12-12</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>3.02亿</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>159677</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>159677</t>
+        </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -5016,9 +5021,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -5038,9 +5043,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -5060,9 +5065,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -5082,9 +5087,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -5104,9 +5109,9 @@
           <t>2018-05-31</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>7.05亿</t>
         </is>
       </c>
     </row>
@@ -5126,9 +5131,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -5148,9 +5153,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -5170,9 +5175,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -5192,9 +5197,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5219,6 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="11.1328125" bestFit="1" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5255,9 +5259,9 @@
           <t>2025-03-20</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>670.64万</t>
         </is>
       </c>
     </row>
@@ -5277,9 +5281,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -5299,9 +5303,9 @@
           <t>2025-09-16</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6.98亿</t>
         </is>
       </c>
     </row>
@@ -5321,9 +5325,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -5343,9 +5347,9 @@
           <t>2025-11-12</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1.70亿</t>
         </is>
       </c>
     </row>
@@ -5365,9 +5369,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1002.50万</t>
         </is>
       </c>
     </row>
@@ -5387,9 +5391,9 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>5178.20万</t>
         </is>
       </c>
     </row>
@@ -5409,9 +5413,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -5431,9 +5435,9 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2237.80万</t>
         </is>
       </c>
     </row>
@@ -5453,9 +5457,9 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6147.03万</t>
         </is>
       </c>
     </row>
@@ -5475,9 +5479,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -5497,9 +5501,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -5519,9 +5523,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -5541,9 +5545,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -5563,9 +5567,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>
@@ -5585,9 +5589,9 @@
           <t>获取失败</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>待补充</t>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>获取失败</t>
         </is>
       </c>
     </row>

--- a/data/fund_whitelist.xlsx
+++ b/data/fund_whitelist.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="沪深300" sheetId="1" state="visible" r:id="rId1"/>
@@ -42,7 +42,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -53,12 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1A2E3D"/>
         <bgColor rgb="FF1A2E3D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -86,7 +80,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -457,6 +451,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="11.1328125" bestFit="1" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -565,7 +560,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7112.58万</t>
+          <t>0.71亿</t>
         </is>
       </c>
     </row>
@@ -719,7 +714,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9869.45万</t>
+          <t>0.99亿</t>
         </is>
       </c>
     </row>
@@ -895,7 +890,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7464.89万</t>
+          <t>0.75亿</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1176,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4036.62万</t>
+          <t>0.40亿</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1198,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8120.31万</t>
+          <t>0.81亿</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1220,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>6496.02万</t>
+          <t>0.65亿</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1242,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2523.15万</t>
+          <t>0.25亿</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1264,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2688.43万</t>
+          <t>0.27亿</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1286,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1280.40万</t>
+          <t>0.13亿</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1352,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2785.47万</t>
+          <t>0.28亿</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1462,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1519.04万</t>
+          <t>0.15亿</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1484,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2781.16万</t>
+          <t>0.28亿</t>
         </is>
       </c>
     </row>
@@ -1526,14 +1521,12 @@
           <t>贝莱德沪深300指数增强A</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C49" s="3" t="n">
+        <v>45622</v>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>2.00亿</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1570,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3143.65万</t>
+          <t>0.31亿</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1592,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>4805.47万</t>
+          <t>0.48亿</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1614,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2345.43万</t>
+          <t>0.23亿</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1636,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2234.59万</t>
+          <t>0.22亿</t>
         </is>
       </c>
     </row>
@@ -1658,14 +1651,12 @@
           <t>长信沪深300指数量化增强A</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C55" s="3" t="n">
+        <v>45891</v>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>1.97亿</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1678,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2647.94万</t>
+          <t>0.26亿</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1700,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1959.58万</t>
+          <t>0.20亿</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1722,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>3375.37万</t>
+          <t>0.34亿</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1744,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>737.52万</t>
+          <t>0.07亿</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1810,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1372.07万</t>
+          <t>0.14亿</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1832,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1363.58万</t>
+          <t>0.14亿</t>
         </is>
       </c>
     </row>
@@ -1878,14 +1869,12 @@
           <t>德邦沪深300指数增强A</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C65" s="3" t="n">
+        <v>46065</v>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>2.20亿</t>
         </is>
       </c>
     </row>
@@ -1900,14 +1889,12 @@
           <t>华泰保兴沪深300指数增强A</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C66" s="3" t="n">
+        <v>46149</v>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>1.05亿</t>
         </is>
       </c>
     </row>
@@ -1966,14 +1953,12 @@
           <t>景顺长城沪深300增强策略ETF</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C69" s="3" t="n">
+        <v>45805</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>0.54亿</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2068,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>9469.08万</t>
+          <t>0.95亿</t>
         </is>
       </c>
     </row>
@@ -2208,14 +2193,12 @@
           <t>华安沪深300增强策略ETF</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C80" s="3" t="n">
+        <v>44916</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>0.64亿</t>
         </is>
       </c>
     </row>
@@ -2230,14 +2213,12 @@
           <t>国泰沪深300增强策略ETF</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C81" s="3" t="n">
+        <v>44531</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>3.88亿</t>
         </is>
       </c>
     </row>
@@ -2252,14 +2233,12 @@
           <t>招商沪深300增强策略ETF</t>
         </is>
       </c>
-      <c r="C82" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D82" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C82" s="3" t="n">
+        <v>44532</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>3.47亿</t>
         </is>
       </c>
     </row>
@@ -2274,14 +2253,12 @@
           <t>华宝沪深300增强策略ETF</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C83" s="3" t="n">
+        <v>46008</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>4.56亿</t>
         </is>
       </c>
     </row>
@@ -2323,6 +2300,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="11.1328125" bestFit="1" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2409,7 +2387,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2758.73万</t>
+          <t>0.28亿</t>
         </is>
       </c>
     </row>
@@ -2563,7 +2541,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8243.26万</t>
+          <t>0.82亿</t>
         </is>
       </c>
     </row>
@@ -2673,7 +2651,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3092.56万</t>
+          <t>0.31亿</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2673,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1156.65万</t>
+          <t>0.12亿</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2739,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>9843.42万</t>
+          <t>0.98亿</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2827,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7830.15万</t>
+          <t>0.78亿</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2871,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>7786.00万</t>
+          <t>0.78亿</t>
         </is>
       </c>
     </row>
@@ -2915,7 +2893,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1390.64万</t>
+          <t>0.14亿</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2937,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3629.30万</t>
+          <t>0.36亿</t>
         </is>
       </c>
     </row>
@@ -3003,7 +2981,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1897.09万</t>
+          <t>0.19亿</t>
         </is>
       </c>
     </row>
@@ -3018,14 +2996,12 @@
           <t>汇安中证500增强A</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C32" s="3" t="n">
+        <v>44151</v>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>0.40亿</t>
         </is>
       </c>
     </row>
@@ -3047,7 +3023,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2701.93万</t>
+          <t>0.27亿</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3067,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4901.87万</t>
+          <t>0.49亿</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3089,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3505.66万</t>
+          <t>0.35亿</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3155,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>9277.21万</t>
+          <t>0.93亿</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3177,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8935.54万</t>
+          <t>0.89亿</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3265,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>4339.94万</t>
+          <t>0.43亿</t>
         </is>
       </c>
     </row>
@@ -3377,7 +3353,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>559.34万</t>
+          <t>0.06亿</t>
         </is>
       </c>
     </row>
@@ -3399,7 +3375,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3486.24万</t>
+          <t>0.35亿</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3397,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2161.54万</t>
+          <t>0.22亿</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3419,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2935.08万</t>
+          <t>0.29亿</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3441,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2027.83万</t>
+          <t>0.20亿</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3485,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1905.22万</t>
+          <t>0.19亿</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3507,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>3421.12万</t>
+          <t>0.34亿</t>
         </is>
       </c>
     </row>
@@ -3553,7 +3529,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>7240.92万</t>
+          <t>0.72亿</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3551,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2143.25万</t>
+          <t>0.21亿</t>
         </is>
       </c>
     </row>
@@ -3590,14 +3566,12 @@
           <t>苏新中证500指数增强A</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C58" s="3" t="n">
+        <v>45656</v>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>1.41亿</t>
         </is>
       </c>
     </row>
@@ -3634,14 +3608,12 @@
           <t>招商资管中证500指数增强A</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C60" s="3" t="n">
+        <v>45673</v>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>0.20亿</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3635,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>6399.46万</t>
+          <t>0.64亿</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3657,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>7658.44万</t>
+          <t>0.77亿</t>
         </is>
       </c>
     </row>
@@ -3700,14 +3672,12 @@
           <t>招商中证500增强策略ETF联接A</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C63" s="3" t="n">
+        <v>45902</v>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>0.29亿</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3699,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3856.85万</t>
+          <t>0.39亿</t>
         </is>
       </c>
     </row>
@@ -3766,14 +3736,12 @@
           <t>贝莱德中证500指数增强A</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C66" s="3" t="n">
+        <v>45926</v>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>1.14亿</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3763,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>3404.98万</t>
+          <t>0.34亿</t>
         </is>
       </c>
     </row>
@@ -3810,14 +3778,12 @@
           <t>联博中证500指数增强A</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C68" s="3" t="n">
+        <v>46000</v>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>1.30亿</t>
         </is>
       </c>
     </row>
@@ -3839,7 +3805,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>8088.65万</t>
+          <t>0.81亿</t>
         </is>
       </c>
     </row>
@@ -3876,14 +3842,12 @@
           <t>中欧中证500指数量化增强A</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C71" s="3" t="n">
+        <v>46149</v>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>9.09亿</t>
         </is>
       </c>
     </row>
@@ -3898,14 +3862,12 @@
           <t>景顺长城中证500增强策略ETF</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C72" s="3" t="n">
+        <v>44543</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2.05亿</t>
         </is>
       </c>
     </row>
@@ -3920,14 +3882,12 @@
           <t>博时中证500增强策略ETF</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C73" s="3" t="n">
+        <v>44970</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1.42亿</t>
         </is>
       </c>
     </row>
@@ -4015,7 +3975,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2978.59万</t>
+          <t>0.30亿</t>
         </is>
       </c>
     </row>
@@ -4030,14 +3990,12 @@
           <t>南方中证500增强策略ETF</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C78" s="3" t="n">
+        <v>44587</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>0.90亿</t>
         </is>
       </c>
     </row>
@@ -4052,14 +4010,12 @@
           <t>汇添富中证500增强策略ETF</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C79" s="3" t="n">
+        <v>45126</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>0.20亿</t>
         </is>
       </c>
     </row>
@@ -4074,14 +4030,12 @@
           <t>华泰柏瑞中证500增强策略ETF</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C80" s="3" t="n">
+        <v>44532</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>16.70亿</t>
         </is>
       </c>
     </row>
@@ -4096,14 +4050,12 @@
           <t>招商中证500增强策略ETF</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C81" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1.16亿</t>
         </is>
       </c>
     </row>
@@ -4118,14 +4070,12 @@
           <t>易方达中证500增强策略ETF</t>
         </is>
       </c>
-      <c r="C82" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D82" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C82" s="3" t="n">
+        <v>44974</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1.71亿</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4097,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>5731.22万</t>
+          <t>0.57亿</t>
         </is>
       </c>
     </row>
@@ -4167,6 +4117,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="11.1328125" bestFit="1" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4209,7 +4160,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3575.34万</t>
+          <t>0.36亿</t>
         </is>
       </c>
     </row>
@@ -4341,7 +4292,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7012.16万</t>
+          <t>0.70亿</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4314,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2867.73万</t>
+          <t>0.29亿</t>
         </is>
       </c>
     </row>
@@ -4407,7 +4358,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4686.89万</t>
+          <t>0.47亿</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4424,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5529.41万</t>
+          <t>0.55亿</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4534,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3756.60万</t>
+          <t>0.38亿</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4600,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1350.89万</t>
+          <t>0.14亿</t>
         </is>
       </c>
     </row>
@@ -4664,14 +4615,12 @@
           <t>明亚中证1000指数增强A</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C23" s="3" t="n">
+        <v>45041</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0.01亿</t>
         </is>
       </c>
     </row>
@@ -4825,7 +4774,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1698.95万</t>
+          <t>0.17亿</t>
         </is>
       </c>
     </row>
@@ -4869,7 +4818,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1012.36万</t>
+          <t>0.10亿</t>
         </is>
       </c>
     </row>
@@ -4891,7 +4840,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>7929.09万</t>
+          <t>0.79亿</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4862,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1683.44万</t>
+          <t>0.17亿</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4906,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>453.93万</t>
+          <t>0.05亿</t>
         </is>
       </c>
     </row>
@@ -4979,7 +4928,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1038.82万</t>
+          <t>0.10亿</t>
         </is>
       </c>
     </row>
@@ -5016,14 +4965,12 @@
           <t>银华中证1000增强策略ETF</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C39" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>0.44亿</t>
         </is>
       </c>
     </row>
@@ -5038,14 +4985,12 @@
           <t>国泰中证1000增强策略ETF</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C40" s="3" t="n">
+        <v>44966</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>0.63亿</t>
         </is>
       </c>
     </row>
@@ -5060,14 +5005,12 @@
           <t>招商中证1000增强策略ETF</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C41" s="3" t="n">
+        <v>44883</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>14.68亿</t>
         </is>
       </c>
     </row>
@@ -5082,14 +5025,12 @@
           <t>天弘中证1000增强策略ETF</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C42" s="3" t="n">
+        <v>45000</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>0.22亿</t>
         </is>
       </c>
     </row>
@@ -5126,14 +5067,12 @@
           <t>鹏华中证1000增强策略ETF</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C44" s="3" t="n">
+        <v>45170</v>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>0.22亿</t>
         </is>
       </c>
     </row>
@@ -5148,14 +5087,12 @@
           <t>工银中证1000增强策略ETF</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C45" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1.30亿</t>
         </is>
       </c>
     </row>
@@ -5170,14 +5107,12 @@
           <t>华泰柏瑞中证1000增强策略ETF</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C46" s="3" t="n">
+        <v>44888</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1.27亿</t>
         </is>
       </c>
     </row>
@@ -5192,14 +5127,12 @@
           <t>博时中证1000增强策略ETF</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C47" s="3" t="n">
+        <v>45232</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.20亿</t>
         </is>
       </c>
     </row>
@@ -5219,6 +5152,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="11.1328125" bestFit="1" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5261,7 +5195,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>670.64万</t>
+          <t>0.07亿</t>
         </is>
       </c>
     </row>
@@ -5276,14 +5210,12 @@
           <t>博道中证全指指数增强A</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C3" s="3" t="n">
+        <v>45909</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>1.15亿</t>
         </is>
       </c>
     </row>
@@ -5320,14 +5252,12 @@
           <t>国泰海通中证全指指数增强A</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C5" s="3" t="n">
+        <v>45993</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0.88亿</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5301,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1002.50万</t>
+          <t>0.10亿</t>
         </is>
       </c>
     </row>
@@ -5393,7 +5323,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5178.20万</t>
+          <t>0.52亿</t>
         </is>
       </c>
     </row>
@@ -5408,14 +5338,12 @@
           <t>长江中证全指指数增强A</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C9" s="3" t="n">
+        <v>46020</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0.34亿</t>
         </is>
       </c>
     </row>
@@ -5437,7 +5365,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2237.80万</t>
+          <t>0.22亿</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5387,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6147.03万</t>
+          <t>0.61亿</t>
         </is>
       </c>
     </row>
@@ -5474,14 +5402,12 @@
           <t>兴全中证全指增强A</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C12" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0.47亿</t>
         </is>
       </c>
     </row>
@@ -5496,14 +5422,12 @@
           <t>浙商中证全指指数增强A</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C13" s="3" t="n">
+        <v>46170</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1.25亿</t>
         </is>
       </c>
     </row>
@@ -5518,14 +5442,12 @@
           <t>兴业中证全指指数增强A</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C14" s="3" t="n">
+        <v>46202</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8.52亿</t>
         </is>
       </c>
     </row>
@@ -5540,14 +5462,12 @@
           <t>宏利中证全指指数增强A</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C15" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>7.69亿</t>
         </is>
       </c>
     </row>
@@ -5562,14 +5482,12 @@
           <t>东兴中证全指指数量化增强A</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C16" s="3" t="n">
+        <v>46196</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2.36亿</t>
         </is>
       </c>
     </row>
@@ -5584,14 +5502,12 @@
           <t>太平中证全指指数增强A</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>获取失败</t>
+      <c r="C17" s="3" t="n">
+        <v>46217</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3.10亿</t>
         </is>
       </c>
     </row>
